--- a/data/trans_bre/P57_AF_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 15,11</t>
+          <t>1,99; 14,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 17,99</t>
+          <t>2,41; 18,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 14,18</t>
+          <t>-1,45; 14,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 16,08</t>
+          <t>-1,27; 15,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 20,67</t>
+          <t>2,46; 20,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 29,02</t>
+          <t>3,37; 29,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 23,26</t>
+          <t>-2,03; 23,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 41,06</t>
+          <t>-2,36; 39,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 10,05</t>
+          <t>-3,44; 9,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 7,39</t>
+          <t>-6,04; 6,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 5,52</t>
+          <t>-4,46; 5,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 4,49</t>
+          <t>-9,36; 4,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 18,12</t>
+          <t>-5,42; 16,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 15,53</t>
+          <t>-11,07; 14,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 7,01</t>
+          <t>-5,34; 7,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 8,89</t>
+          <t>-15,64; 9,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 2,82</t>
+          <t>-13,78; 2,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 16,36</t>
+          <t>0,79; 15,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 10,08</t>
+          <t>-3,14; 10,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 14,6</t>
+          <t>-0,34; 14,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 6,61</t>
+          <t>-27,03; 5,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 30,08</t>
+          <t>1,29; 28,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 14,71</t>
+          <t>-4,17; 14,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 41,3</t>
+          <t>-0,66; 41,25</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 5,39</t>
+          <t>-8,89; 5,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 16,16</t>
+          <t>1,82; 16,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 10,85</t>
+          <t>-3,55; 10,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 7,05</t>
+          <t>-12,06; 7,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 9,13</t>
+          <t>-13,35; 8,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 38,73</t>
+          <t>3,5; 38,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 33,41</t>
+          <t>-9,03; 35,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,52; 31,43</t>
+          <t>-43,7; 30,64</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 14,79</t>
+          <t>-2,15; 14,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 24,06</t>
+          <t>4,56; 23,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,87</t>
+          <t>-6,08; 7,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 5,05</t>
+          <t>-5,4; 4,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 24,02</t>
+          <t>-2,83; 24,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 51,95</t>
+          <t>7,47; 50,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 9,64</t>
+          <t>-6,89; 9,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 5,66</t>
+          <t>-5,73; 5,47</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 4,96</t>
+          <t>-11,58; 5,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 16,98</t>
+          <t>0,52; 17,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 12,02</t>
+          <t>-2,55; 11,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 7,65</t>
+          <t>-6,12; 7,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 8,89</t>
+          <t>-18,29; 9,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 30,73</t>
+          <t>1,02; 32,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 17,81</t>
+          <t>-3,43; 17,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 24,05</t>
+          <t>-15,32; 23,32</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -1,06</t>
+          <t>-12,68; -1,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 10,67</t>
+          <t>0,12; 11,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 2,32</t>
+          <t>-7,45; 2,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 31,21</t>
+          <t>-5,35; 28,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,58; -3,39</t>
+          <t>-27,96; -4,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 20,07</t>
+          <t>0,23; 21,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 2,91</t>
+          <t>-9,1; 3,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 60,57</t>
+          <t>-9,33; 58,49</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,9</t>
+          <t>2,11; 11,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 1,39</t>
+          <t>-6,1; 1,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 7,44</t>
+          <t>-0,01; 6,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 60,32</t>
+          <t>2,01; 56,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,49; 15,56</t>
+          <t>2,76; 15,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,64</t>
+          <t>-6,95; 1,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 9,07</t>
+          <t>0,0; 8,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,22; 237,29</t>
+          <t>2,55; 195,39</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,99</t>
+          <t>-1,92; 3,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,32</t>
+          <t>2,54; 7,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,3</t>
+          <t>0,08; 4,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 19,88</t>
+          <t>0,3; 19,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,02</t>
+          <t>-3,07; 5,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,94; 12,06</t>
+          <t>3,96; 12,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,9</t>
+          <t>0,1; 5,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 47,02</t>
+          <t>0,67; 43,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AF_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 14,98</t>
+          <t>1,93; 14,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 18,19</t>
+          <t>2,74; 18,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 14,19</t>
+          <t>-1,95; 13,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 15,96</t>
+          <t>-2,96; 11,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 20,53</t>
+          <t>2,34; 19,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 29,84</t>
+          <t>4,06; 31,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 23,16</t>
+          <t>-2,68; 21,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 39,79</t>
+          <t>-5,75; 25,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,62%</t>
+          <t>-5,69%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 9,21</t>
+          <t>-2,78; 9,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 6,86</t>
+          <t>-5,65; 7,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 5,77</t>
+          <t>-4,41; 5,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 4,66</t>
+          <t>-9,99; 3,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 16,27</t>
+          <t>-4,26; 17,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 14,29</t>
+          <t>-10,32; 15,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 7,48</t>
+          <t>-5,33; 7,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 9,03</t>
+          <t>-16,74; 7,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 2,46</t>
+          <t>-13,19; 2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 15,42</t>
+          <t>0,35; 15,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 10,29</t>
+          <t>-3,51; 9,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 14,65</t>
+          <t>0,22; 15,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 5,9</t>
+          <t>-25,63; 6,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 28,19</t>
+          <t>0,55; 29,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 14,99</t>
+          <t>-4,55; 14,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 41,25</t>
+          <t>-0,25; 41,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,99%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 5,03</t>
+          <t>-10,09; 4,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 16,23</t>
+          <t>1,19; 16,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 10,9</t>
+          <t>-3,18; 11,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 7,09</t>
+          <t>-2,14; 11,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 8,07</t>
+          <t>-14,88; 8,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 38,7</t>
+          <t>2,37; 37,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 35,43</t>
+          <t>-7,68; 37,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,7; 30,64</t>
+          <t>-7,41; 56,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,39%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 14,84</t>
+          <t>-3,12; 14,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 23,66</t>
+          <t>5,22; 24,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 7,6</t>
+          <t>-5,96; 7,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,83</t>
+          <t>-3,97; 6,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 24,1</t>
+          <t>-4,16; 23,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 50,92</t>
+          <t>8,87; 50,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 9,22</t>
+          <t>-6,69; 9,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 5,47</t>
+          <t>-4,25; 7,19</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 5,19</t>
+          <t>-11,54; 5,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 17,37</t>
+          <t>0,26; 17,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 11,97</t>
+          <t>-2,91; 11,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 7,58</t>
+          <t>-6,12; 6,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 9,65</t>
+          <t>-18,64; 9,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 32,54</t>
+          <t>1,13; 32,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 17,94</t>
+          <t>-3,73; 17,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 23,32</t>
+          <t>-14,56; 20,18</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>-2,4</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>-4,36%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,68; -1,82</t>
+          <t>-12,92; -1,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 11,37</t>
+          <t>0,16; 10,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,49</t>
+          <t>-6,63; 2,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 28,85</t>
+          <t>-8,4; 3,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,96; -4,41</t>
+          <t>-28,0; -4,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 21,69</t>
+          <t>0,22; 20,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 3,29</t>
+          <t>-8,19; 3,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 58,49</t>
+          <t>-14,32; 5,98</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24,77</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,09</t>
+          <t>2,31; 10,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,46</t>
+          <t>-6,04; 1,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 6,88</t>
+          <t>0,11; 7,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,01; 56,85</t>
+          <t>-1,23; 6,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 15,79</t>
+          <t>3,1; 15,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 1,75</t>
+          <t>-6,9; 1,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,39</t>
+          <t>0,1; 8,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 195,39</t>
+          <t>-1,41; 8,46</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,05</t>
+          <t>-1,87; 3,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,36</t>
+          <t>2,64; 7,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,17</t>
+          <t>0,05; 4,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 19,56</t>
+          <t>-1,28; 3,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,14</t>
+          <t>-3,0; 5,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,96; 12,19</t>
+          <t>4,16; 12,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 5,7</t>
+          <t>0,07; 5,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 43,49</t>
+          <t>-2,16; 6,37</t>
         </is>
       </c>
     </row>
